--- a/artfynd/A 42193-2024 artfynd.xlsx
+++ b/artfynd/A 42193-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -887,6 +887,412 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128785527</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90093</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4962</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mjölsvärting</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lyophyllum semitale</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>753845</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7092716</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128785509</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92772</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>753787</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7092685</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128785530</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92756</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>753829</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7092672</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128785507</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92760</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>753891</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7092763</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Under mossbevuxen tallåga</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42193-2024 artfynd.xlsx
+++ b/artfynd/A 42193-2024 artfynd.xlsx
@@ -993,7 +993,7 @@
         <v>128785509</v>
       </c>
       <c r="B5" t="n">
-        <v>92772</v>
+        <v>92773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128785530</v>
       </c>
       <c r="B6" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>128785507</v>
       </c>
       <c r="B7" t="n">
-        <v>92760</v>
+        <v>92761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 42193-2024 artfynd.xlsx
+++ b/artfynd/A 42193-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128729308</v>
       </c>
       <c r="B2" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128729372</v>
       </c>
       <c r="B3" t="n">
-        <v>90093</v>
+        <v>90120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128785527</v>
       </c>
       <c r="B4" t="n">
-        <v>90093</v>
+        <v>90120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>128785509</v>
       </c>
       <c r="B5" t="n">
-        <v>92773</v>
+        <v>92800</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128785530</v>
       </c>
       <c r="B6" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>128785507</v>
       </c>
       <c r="B7" t="n">
-        <v>92761</v>
+        <v>92788</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 42193-2024 artfynd.xlsx
+++ b/artfynd/A 42193-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>128729372</v>
       </c>
       <c r="B3" t="n">
-        <v>90120</v>
+        <v>90125</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128785527</v>
       </c>
       <c r="B4" t="n">
-        <v>90120</v>
+        <v>90125</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>128785509</v>
       </c>
       <c r="B5" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128785530</v>
       </c>
       <c r="B6" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>128785507</v>
       </c>
       <c r="B7" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 42193-2024 artfynd.xlsx
+++ b/artfynd/A 42193-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>128729372</v>
       </c>
       <c r="B3" t="n">
-        <v>90125</v>
+        <v>90130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128785527</v>
       </c>
       <c r="B4" t="n">
-        <v>90125</v>
+        <v>90130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>128785509</v>
       </c>
       <c r="B5" t="n">
-        <v>92805</v>
+        <v>92810</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128785530</v>
       </c>
       <c r="B6" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>128785507</v>
       </c>
       <c r="B7" t="n">
-        <v>92793</v>
+        <v>92798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 42193-2024 artfynd.xlsx
+++ b/artfynd/A 42193-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128729308</v>
       </c>
       <c r="B2" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128729372</v>
       </c>
       <c r="B3" t="n">
-        <v>90130</v>
+        <v>90134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128785527</v>
       </c>
       <c r="B4" t="n">
-        <v>90130</v>
+        <v>90134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>128785509</v>
       </c>
       <c r="B5" t="n">
-        <v>92810</v>
+        <v>92814</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128785530</v>
       </c>
       <c r="B6" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>128785507</v>
       </c>
       <c r="B7" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 42193-2024 artfynd.xlsx
+++ b/artfynd/A 42193-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128729308</v>
       </c>
       <c r="B2" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128729372</v>
       </c>
       <c r="B3" t="n">
-        <v>90134</v>
+        <v>90139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128785527</v>
       </c>
       <c r="B4" t="n">
-        <v>90134</v>
+        <v>90139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>128785509</v>
       </c>
       <c r="B5" t="n">
-        <v>92814</v>
+        <v>92819</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128785530</v>
       </c>
       <c r="B6" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>128785507</v>
       </c>
       <c r="B7" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 42193-2024 artfynd.xlsx
+++ b/artfynd/A 42193-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>128729372</v>
       </c>
       <c r="B3" t="n">
-        <v>90146</v>
+        <v>90149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128785527</v>
       </c>
       <c r="B4" t="n">
-        <v>90146</v>
+        <v>90149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>128785509</v>
       </c>
       <c r="B5" t="n">
-        <v>92827</v>
+        <v>92832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128785530</v>
       </c>
       <c r="B6" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>128785507</v>
       </c>
       <c r="B7" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 42193-2024 artfynd.xlsx
+++ b/artfynd/A 42193-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>128729372</v>
       </c>
       <c r="B3" t="n">
-        <v>90149</v>
+        <v>90152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128785527</v>
       </c>
       <c r="B4" t="n">
-        <v>90149</v>
+        <v>90152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>128785509</v>
       </c>
       <c r="B5" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128785530</v>
       </c>
       <c r="B6" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>128785507</v>
       </c>
       <c r="B7" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 42193-2024 artfynd.xlsx
+++ b/artfynd/A 42193-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128729308</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128729372</v>
       </c>
       <c r="B3" t="n">
-        <v>90152</v>
+        <v>90156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128785527</v>
       </c>
       <c r="B4" t="n">
-        <v>90152</v>
+        <v>90156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>128785509</v>
       </c>
       <c r="B5" t="n">
-        <v>92835</v>
+        <v>92842</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128785530</v>
       </c>
       <c r="B6" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>128785507</v>
       </c>
       <c r="B7" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 42193-2024 artfynd.xlsx
+++ b/artfynd/A 42193-2024 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>128785527</v>
       </c>
       <c r="B4" t="n">
-        <v>90156</v>
+        <v>90163</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>128785509</v>
       </c>
       <c r="B5" t="n">
-        <v>92842</v>
+        <v>92849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128785530</v>
       </c>
       <c r="B6" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>128785507</v>
       </c>
       <c r="B7" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 42193-2024 artfynd.xlsx
+++ b/artfynd/A 42193-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128729308</v>
       </c>
       <c r="B2" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128729372</v>
       </c>
       <c r="B3" t="n">
-        <v>90156</v>
+        <v>90165</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128785527</v>
       </c>
       <c r="B4" t="n">
-        <v>90163</v>
+        <v>90165</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>128785509</v>
       </c>
       <c r="B5" t="n">
-        <v>92849</v>
+        <v>92851</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128785530</v>
       </c>
       <c r="B6" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>128785507</v>
       </c>
       <c r="B7" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 42193-2024 artfynd.xlsx
+++ b/artfynd/A 42193-2024 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>128785527</v>
       </c>
       <c r="B4" t="n">
-        <v>90165</v>
+        <v>90166</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>128785509</v>
       </c>
       <c r="B5" t="n">
-        <v>92851</v>
+        <v>92837</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128785530</v>
       </c>
       <c r="B6" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>128785507</v>
       </c>
       <c r="B7" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 42193-2024 artfynd.xlsx
+++ b/artfynd/A 42193-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128729308</v>
+        <v>128785509</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Forslunda Vattenverk, Umeå, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>753833</v>
+        <v>753787</v>
       </c>
       <c r="R2" t="n">
-        <v>7092744</v>
+        <v>7092685</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,19 +747,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,60 +764,64 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128729372</v>
+        <v>128785511</v>
       </c>
       <c r="B3" t="n">
-        <v>90165</v>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4962</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>753842</v>
+        <v>753948</v>
       </c>
       <c r="R3" t="n">
-        <v>7092749</v>
+        <v>7092786</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,19 +848,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +865,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128785527</v>
+        <v>128785530</v>
       </c>
       <c r="B4" t="n">
-        <v>90166</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,38 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753845</v>
+        <v>753829</v>
       </c>
       <c r="R4" t="n">
-        <v>7092716</v>
+        <v>7092672</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -964,6 +948,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,49 +979,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128785509</v>
+        <v>128785503</v>
       </c>
       <c r="B5" t="n">
-        <v>92837</v>
+        <v>93201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>4365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>753787</v>
+        <v>753997</v>
       </c>
       <c r="R5" t="n">
-        <v>7092685</v>
+        <v>7092750</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1065,6 +1050,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Under tunn tallåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,32 +1081,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128785530</v>
+        <v>128785507</v>
       </c>
       <c r="B6" t="n">
-        <v>92821</v>
+        <v>93201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1126,10 +1116,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>753829</v>
+        <v>753891</v>
       </c>
       <c r="R6" t="n">
-        <v>7092672</v>
+        <v>7092763</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1166,7 +1156,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Fjolårets fruktkroppar</t>
+          <t>Under mossbevuxen tallåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,48 +1183,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128785507</v>
+        <v>128729372</v>
       </c>
       <c r="B7" t="n">
-        <v>92825</v>
+        <v>90522</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>4962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>753891</v>
+        <v>753842</v>
       </c>
       <c r="R7" t="n">
-        <v>7092763</v>
+        <v>7092749</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1261,14 +1251,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Under mossbevuxen tallåga</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1283,15 +1278,223 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128785527</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90522</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4962</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mjölsvärting</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lyophyllum semitale</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>753845</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7092716</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Roger Olofsson</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Roger Olofsson</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128729308</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Forslunda Vattenverk, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>753833</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7092744</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42193-2024 artfynd.xlsx
+++ b/artfynd/A 42193-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128785509</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128785511</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128785530</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128785503</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128785507</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1287,6 +1317,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128729372</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1388,6 +1423,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128785527</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1495,8 +1535,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128729308</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>